--- a/Assessment Questions/AIE/DBM-120/SQL Basics/MySQL Workbench Installation/Workbench_Scenario_Proper.xlsx
+++ b/Assessment Questions/AIE/DBM-120/SQL Basics/MySQL Workbench Installation/Workbench_Scenario_Proper.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workbench Scenario MCQs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,37 +424,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Scenario Question</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Scenario Question</t>
+          <t>Option A</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Option B</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Option C</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>Option D</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Option D</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -464,37 +459,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You are configuring a new MySQL connection in MySQL Workbench. The server is running on default settings. Which port number should you enter to successfully connect?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>You are configuring a new MySQL connection in MySQL Workbench. The server is running on default settings. Which port number should you enter to successfully connect?</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>5432</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5432</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1521</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3306</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -504,37 +494,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>While writing a query in MySQL Workbench, you want to execute only a selected portion of the SQL code instead of the entire script. Which option or shortcut should you use?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>While writing a query in MySQL Workbench, you want to execute only a selected portion of the SQL code instead of the entire script. Which option or shortcut should you use?</t>
+          <t>Execute Selection (Ctrl+Enter)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Execute Selection (Ctrl+Enter)</t>
+          <t>Run All</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Run All</t>
+          <t>Compile</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Compile</t>
+          <t>Debug</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Debug</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Execute Selection (Ctrl+Enter)</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -544,37 +529,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>After executing a SELECT query in MySQL Workbench, you are unable to see the output. Where should you look to view the query results?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>After executing a SELECT query in MySQL Workbench, you are unable to see the output. Where should you look to view the query results?</t>
+          <t>Result Grid</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Result Grid</t>
+          <t>Navigator</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Navigator</t>
+          <t>Logs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Logs</t>
+          <t>Editor</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Editor</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Result Grid</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -584,37 +564,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>A user is unable to connect to the MySQL server from Workbench. What is the first thing they should verify before troubleshooting further?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A user is unable to connect to the MySQL server from Workbench. What is the first thing they should verify before troubleshooting further?</t>
+          <t>Check if MySQL server is running</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Check if MySQL server is running</t>
+          <t>Rewrite the query</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rewrite the query</t>
+          <t>Restart system</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Restart system</t>
+          <t>Change UI theme</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Change UI theme</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Check if MySQL server is running</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -624,37 +599,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You need to import a dataset from a dump file into MySQL Workbench for analysis. Which feature should you use?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>You need to import a dataset from a dump file into MySQL Workbench for analysis. Which feature should you use?</t>
+          <t>Data Import</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Data Import</t>
+          <t>SQL Editor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SQL Editor</t>
+          <t>Navigator Panel</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
+          <t>Server Logs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Server Logs</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Data Import</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -664,37 +634,32 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You want to create a backup of an existing database in MySQL Workbench. Which feature should you use?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>You want to create a backup of an existing database in MySQL Workbench. Which feature should you use?</t>
+          <t>Data Export</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Data Export</t>
+          <t>Save Query</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Save Query</t>
+          <t>Transfer Wizard</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Transfer Wizard</t>
+          <t>Logs Panel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Logs Panel</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Data Export</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -704,37 +669,32 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>While exploring a database schema, you want to view all tables and their structure. Which panel in MySQL Workbench should you use?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>While exploring a database schema, you want to view all tables and their structure. Which panel in MySQL Workbench should you use?</t>
+          <t>Navigator Panel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
+          <t>Output Panel</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Output Panel</t>
+          <t>Logs Panel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Logs Panel</t>
+          <t>Editor Panel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Editor Panel</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Navigator Panel</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -744,37 +704,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You need to modify the structure of an existing table by adding a new column. Which SQL operation should you perform in MySQL Workbench?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>You need to modify the structure of an existing table by adding a new column. Which SQL operation should you perform in MySQL Workbench?</t>
+          <t>ALTER TABLE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ALTER TABLE</t>
+          <t>UPDATE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UPDATE</t>
+          <t>INSERT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>INSERT</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ALTER TABLE</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -784,37 +739,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You want to review previously executed queries in MySQL Workbench for debugging purposes. Where can you find this information?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>You want to review previously executed queries in MySQL Workbench for debugging purposes. Where can you find this information?</t>
+          <t>Query History Panel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Query History Panel</t>
+          <t>Navigator Panel</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
+          <t>Output Panel</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Output Panel</t>
+          <t>Editor Panel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Editor Panel</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Query History Panel</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -824,37 +774,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>While working on multiple queries, you want a quick way to execute the current query without using the mouse. Which shortcut should you use?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>While working on multiple queries, you want a quick way to execute the current query without using the mouse. Which shortcut should you use?</t>
+          <t>Ctrl+Enter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ctrl+Enter</t>
+          <t>Ctrl+S</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ctrl+S</t>
+          <t>Ctrl+Z</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ctrl+Z</t>
+          <t>Ctrl+X</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ctrl+X</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Ctrl+Enter</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -864,37 +809,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>You are connected to a MySQL database, but your queries are failing due to permission issues. What is the most appropriate step to resolve this?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>You are connected to a MySQL database, but your queries are failing due to permission issues. What is the most appropriate step to resolve this?</t>
+          <t>Check user privileges and permissions</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Check user privileges and permissions</t>
+          <t>Restart Workbench</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Restart Workbench</t>
+          <t>Change UI theme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Change UI theme</t>
+          <t>Reinstall MySQL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Reinstall MySQL</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Check user privileges and permissions</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -904,37 +844,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You created a new schema but it is not visible in the list of schemas. What should you do to resolve this issue?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>You created a new schema but it is not visible in the list of schemas. What should you do to resolve this issue?</t>
+          <t>Refresh the Navigator panel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Refresh the Navigator panel</t>
+          <t>Restart system</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Restart system</t>
+          <t>Rewrite query</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rewrite query</t>
+          <t>Reconnect internet</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Reconnect internet</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Refresh the Navigator panel</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -944,37 +879,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>After executing a query, no results are displayed even though the query syntax is correct. What is the most likely reason?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>After executing a query, no results are displayed even though the query syntax is correct. What is the most likely reason?</t>
+          <t>Query conditions do not match any data</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Query conditions do not match any data</t>
+          <t>Workbench error</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Workbench error</t>
+          <t>System crash</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>System crash</t>
+          <t>Port issue</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Port issue</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Query conditions do not match any data</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -984,37 +914,32 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You want to modify only a specific column's datatype in an existing table. Which approach should you take?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>You want to modify only a specific column's datatype in an existing table. Which approach should you take?</t>
+          <t>Use ALTER TABLE with MODIFY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Use ALTER TABLE with MODIFY</t>
+          <t>Drop and recreate table</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Drop and recreate table</t>
+          <t>Insert new values</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Insert new values</t>
+          <t>Select query</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Select query</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Use ALTER TABLE with MODIFY</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1024,37 +949,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>While connecting to a remote MySQL server, which credentials are mandatory for successful authentication?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>While connecting to a remote MySQL server, which credentials are mandatory for successful authentication?</t>
+          <t>Username and Password</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Username and Password</t>
+          <t>Only username</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Only username</t>
+          <t>Only password</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Only password</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Username and Password</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1064,37 +984,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>You notice that your query execution is slower than expected. Which tool in MySQL Workbench can help analyze query performance?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>You notice that your query execution is slower than expected. Which tool in MySQL Workbench can help analyze query performance?</t>
+          <t>Performance/Query Analyzer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Performance/Query Analyzer</t>
+          <t>Navigator Panel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Navigator Panel</t>
+          <t>Logs Panel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Logs Panel</t>
+          <t>Editor Panel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Editor Panel</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Performance/Query Analyzer</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1104,37 +1019,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>If the MySQL service is stopped, what will happen when you try to connect using Workbench?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>If the MySQL service is stopped, what will happen when you try to connect using Workbench?</t>
+          <t>Connection will fail</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Connection will fail</t>
+          <t>Query executes</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Query executes</t>
+          <t>Workbench crashes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Workbench crashes</t>
+          <t>Nothing happens</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nothing happens</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Connection will fail</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1144,37 +1054,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>You want to delete an entire table including its structure from the database. Which SQL command should you use?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>You want to delete an entire table including its structure from the database. Which SQL command should you use?</t>
+          <t>DROP TABLE</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DROP TABLE</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>TRUNCATE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>TRUNCATE</t>
+          <t>REMOVE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>REMOVE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>DROP TABLE</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1184,37 +1089,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>You are connected to the database but unable to execute queries on a specific schema. What is the most appropriate troubleshooting step?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>You are connected to the database but unable to execute queries on a specific schema. What is the most appropriate troubleshooting step?</t>
+          <t>Verify schema selection and permissions</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Verify schema selection and permissions</t>
+          <t>Restart system</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Restart system</t>
+          <t>Change port</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Change port</t>
+          <t>Ignore issue</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ignore issue</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Verify schema selection and permissions</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -1224,37 +1124,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>While working in MySQL Workbench, you want to execute multiple queries sequentially from a script. Which option should you use?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>While working in MySQL Workbench, you want to execute multiple queries sequentially from a script. Which option should you use?</t>
+          <t>Execute All/Run Script</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Execute All/Run Script</t>
+          <t>Execute Selection</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Execute Selection</t>
+          <t>Compile</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Compile</t>
+          <t>Debug</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Debug</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Execute All/Run Script</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
